--- a/reports/telegram/aegis_daily_2026-09-03.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -733,12 +733,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>R2-GNFC-IND-20260806-abf3d2</t>
+          <t>R2-PLTR-USA-20260810-caa9a7</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GNFC_IND_20260806</t>
+          <t>PLTR_USA_20260810</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -775,7 +775,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>80.8</v>
+        <v>73.3</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -783,24 +783,24 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>33.3</v>
+        <v>48.2</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD→STRONG · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · band HOLD · 17d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="n">
-        <v>34.1</v>
+        <v>48.9</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -808,13 +808,13 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>33.1</v>
+        <v>31.7</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z2" s="3" t="n">
         <v>17</v>
@@ -824,57 +824,57 @@
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>576.95</v>
+        <v>169.46</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>553.3</v>
+        <v>169.46</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>571.1799999999999</v>
+        <v>167.77</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>582.72</v>
+        <v>171.15</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>542.33</v>
+        <v>159.29</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>-1.98</v>
+        <v>-6</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>646.1799999999999</v>
+        <v>189.8</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>16.79</v>
+        <v>12</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>715.42</v>
+        <v>210.13</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>29.3</v>
+        <v>24</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>576</v>
+        <v>179.92</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>0.16</v>
+        <v>-5.81</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Value · Trend · Growth</t>
+          <t>Value · Quality · Growth</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr"/>
@@ -886,19 +886,19 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R1-ICICIBANK-IND-20260903-37b65f</t>
+          <t>R2-GDDY-USA-20260903-da4009</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK_IND_20260903</t>
+          <t>GDDY_USA_20260903</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -908,53 +908,59 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>ICICI Bank</t>
-        </is>
-      </c>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.6%) · Rank ↑ 2→1 · Conf 83% · momentum → · 91d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #7 · Conf 49% · band STRONG · 60d left · → HOLD</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>83</v>
+        <v>48.9</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -962,57 +968,63 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="X3" s="3" t="inlineStr"/>
+        <v>28.1</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="n">
-        <v>1426.5</v>
+        <v>101.87</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>1438.5</v>
+        <v>101.87</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1389</v>
+        <v>100.85</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>1464</v>
+        <v>102.89</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>1355.175</v>
+        <v>96.78</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>-5.79</v>
+        <v>-5</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>1502</v>
+        <v>110.02</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>4.41</v>
+        <v>8</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>1607.14</v>
+        <v>117.15</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>11.72</v>
+        <v>15</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>1438</v>
+        <v>100.55</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>-0.8</v>
+        <v>1.31</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="3" t="n">
         <v>0</v>
@@ -1020,33 +1032,31 @@
       <c r="AQ3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · Growth · Trend</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-SBIN-IND-20260821-686443</t>
+          <t>R2-GOOG-USA-20260903-5f0aaa</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SBIN_IND_20260821</t>
+          <t>GOOG_USA_20260903</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1056,45 +1066,65 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +5.8pp alpha</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #4 · Conf 71% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #10 · Conf 49% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>71</v>
+        <v>48.9</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1102,91 +1132,93 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="X4" s="3" t="inlineStr"/>
+        <v>25.8</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y4" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>1020.9</v>
+        <v>333.78</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>1020.900024414062</v>
+        <v>333.78</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>989</v>
+        <v>330.44</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1053</v>
+        <v>337.12</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>969.8549999999999</v>
+        <v>317.09</v>
       </c>
       <c r="AH4" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>1102.572</v>
+        <v>360.48</v>
       </c>
       <c r="AJ4" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>1179.75204</v>
+        <v>383.85</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1034.5</v>
+        <v>332.03</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>0.53</v>
+      </c>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Growth · Quality · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="n">
-        <v>8</v>
+        <v>5.85</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-BEL-IND-20260903-857d33</t>
+          <t>R2-GM-USA-20260903-c02966</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BEL_IND_20260903</t>
+          <t>GM_USA_20260903</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1196,53 +1228,65 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Bharat Electronics</t>
-        </is>
-      </c>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +57.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank ↑ 8→6 · Conf 66% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #11 · Conf 30% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>66</v>
+        <v>29.9</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1250,91 +1294,93 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="X5" s="3" t="inlineStr"/>
+        <v>-25.9</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB5" s="3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="n">
-        <v>405.8</v>
+        <v>84.87</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>388.7</v>
+        <v>84.87</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>394</v>
+        <v>84.02</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>418</v>
+        <v>85.72</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>385.51</v>
+        <v>80.63</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>-0.82</v>
+        <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>438.2640000000001</v>
+        <v>91.66</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>12.75</v>
+        <v>8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>468.9424800000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>20.64</v>
+        <v>15</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>411.2</v>
+        <v>85.63</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>-1.33</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>-0.89</v>
+      </c>
+      <c r="AO5" s="3" t="inlineStr"/>
       <c r="AP5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="n">
-        <v>12.75</v>
+        <v>57.63</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-ONGC-IND-20260811-f86a0f</t>
+          <t>R1-PLTR-USA-20260903-4ffe75</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ONGC_IND_20260811</t>
+          <t>PLTR_USA_20260903</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1344,7 +1390,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1354,7 +1400,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -1366,23 +1412,37 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank #7 · Conf 68% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>68</v>
+        <v>48.9</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1390,11 +1450,11 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>56</v>
+        <v>70.5</v>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>90</v>
@@ -1402,79 +1462,79 @@
       <c r="AA6" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+      <c r="AB6" s="3" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>237.5</v>
+        <v>169.46</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>237.5</v>
+        <v>169.46</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>230</v>
+        <v>167.77</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>245</v>
+        <v>171.15</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>225.625</v>
+        <v>160.987</v>
       </c>
       <c r="AH6" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>256.5</v>
+        <v>189.8</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>274.455</v>
+        <v>203.086</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>15.56</v>
+        <v>19.84</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>236.45</v>
+        <v>179.92</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.44</v>
+        <v>-5.81</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR6" s="3" t="inlineStr"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-COALINDIA-IND-20260903-bdd5ae</t>
+          <t>R1-MU-USA-20260903-2c5556</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260903</t>
+          <t>MU_USA_20260903</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1484,7 +1544,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1494,14 +1554,10 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Coal India</t>
-        </is>
-      </c>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1510,27 +1566,37 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.8%) · Rank ↑ 10→9 · Conf 66% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>66</v>
+        <v>48.9</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1538,7 +1604,7 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>52</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
@@ -1552,77 +1618,77 @@
       </c>
       <c r="AB7" s="3" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>417.9</v>
+        <v>956.08</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>411.3</v>
+        <v>956.08</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>406</v>
+        <v>946.52</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>430</v>
+        <v>965.64</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>397.0049999999999</v>
+        <v>908.276</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>-3.48</v>
+        <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>451.332</v>
+        <v>1070.81</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>9.73</v>
+        <v>12</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>482.92524</v>
+        <v>1145.7667</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>17.41</v>
+        <v>19.84</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>401.6</v>
+        <v>933.4400000000001</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>4.05</v>
+        <v>2.43</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AP7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AR7" s="3" t="inlineStr"/>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>9.73</v>
+        <v>12</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-TATASTEEL-IND-20260828-9c799a</t>
+          <t>R1-INCY-USA-20260903-c89a3c</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL_IND_20260828</t>
+          <t>INCY_USA_20260903</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1632,7 +1698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1642,7 +1708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -1654,23 +1720,37 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.2%) · Rank #10 · Conf 63% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>63</v>
+        <v>48.9</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1678,11 +1758,11 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>51</v>
+        <v>67.5</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>90</v>
@@ -1690,79 +1770,79 @@
       <c r="AA8" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="AB8" s="3" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>183.9</v>
+        <v>128.83</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>183.8500061035156</v>
+        <v>128.83</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>178</v>
+        <v>126.25</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>190</v>
+        <v>131.41</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>174.705</v>
+        <v>122.3885</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>-4.97</v>
+        <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>198.612</v>
+        <v>139.1364</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>212.51484</v>
+        <v>148.875948</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>15.59</v>
+        <v>15.56</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>184.07</v>
+        <v>125.01</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-0.12</v>
+        <v>3.06</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR8" s="3" t="inlineStr"/>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-IRCTC-IND-20260903-21e8cc</t>
+          <t>R1-UBER-USA-20260903-97a5e6</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>IRCTC_IND_20260903</t>
+          <t>UBER_USA_20260903</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1772,7 +1852,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1782,43 +1862,49 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.8%) · Rank ↓ 7→11 · Conf 65% · momentum → · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 52% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>65</v>
+        <v>51.6</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1826,7 +1912,7 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>48</v>
+        <v>66.3</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
@@ -1840,43 +1926,43 @@
       </c>
       <c r="AB9" s="3" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>472.6</v>
+        <v>76.45</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>494.35</v>
+        <v>76.45</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>459</v>
+        <v>74.92</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>486</v>
+        <v>77.98</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>448.97</v>
+        <v>72.6275</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>-9.18</v>
+        <v>-5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>510.4080000000001</v>
+        <v>82.566</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>546.1365600000001</v>
+        <v>88.34562000000001</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>10.48</v>
+        <v>15.56</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>481.35</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>-1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="AP9" s="3" t="n">
         <v>0</v>
@@ -1887,30 +1973,30 @@
       <c r="AR9" s="3" t="inlineStr"/>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT9" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
+          <t>R1-HOOD-USA-20260903-0fb470</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT_IND_20260804</t>
+          <t>HOOD_USA_20260903</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1920,53 +2006,59 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Chambal Fert.</t>
-        </is>
-      </c>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>38.3</v>
+        <v>48.9</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -1974,89 +2066,91 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>22.4</v>
+        <v>63.5</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB10" s="3" t="inlineStr"/>
       <c r="AC10" s="3" t="n">
-        <v>443.35</v>
+        <v>106.99</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>443.35</v>
+        <v>106.99</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>438.92</v>
+        <v>104.85</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>447.78</v>
+        <v>109.13</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>421.1825</v>
+        <v>101.6405</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>478.818</v>
+        <v>115.5492</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>509.8525</v>
+        <v>123.637644</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>413.55</v>
+        <v>103.51</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>-0.3</v>
+        <v>3.36</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R2-PNB-IND-20260804-c7957c</t>
+          <t>R1-GDDY-USA-20260903-41a3ad</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260804</t>
+          <t>GDDY_USA_20260903</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2066,53 +2160,59 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Punjab Natl. Bank</t>
-        </is>
-      </c>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 49% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>32.1</v>
+        <v>48.9</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2120,58 +2220,54 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>22.2</v>
+        <v>61.1</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB11" s="3" t="inlineStr"/>
       <c r="AC11" s="3" t="n">
-        <v>113.36</v>
+        <v>101.87</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>113.36</v>
+        <v>101.87</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>112.23</v>
+        <v>99.83</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>114.49</v>
+        <v>103.91</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>107.692</v>
+        <v>96.7765</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>122.4288</v>
+        <v>110.0196</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>130.364</v>
+        <v>117.720972</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>115.22</v>
+        <v>100.55</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>0</v>
@@ -2180,29 +2276,35 @@
         <v>0</v>
       </c>
       <c r="AQ11" s="3" t="n">
-        <v>-2.01</v>
+        <v>0</v>
       </c>
       <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R2-ITC-IND-20260804-a049df</t>
+          <t>R1-OXY-USA-20260903-16a96a</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260804</t>
+          <t>OXY_USA_20260903</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2212,53 +2314,59 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="M12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 55% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>38.3</v>
+        <v>54.6</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2266,89 +2374,91 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.6</v>
+        <v>60.4</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB12" s="3" t="inlineStr"/>
       <c r="AC12" s="3" t="n">
-        <v>282.9</v>
+        <v>60.91</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>282.9</v>
+        <v>60.91</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>280.07</v>
+        <v>59.69</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>285.73</v>
+        <v>62.13</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>268.7549999999999</v>
+        <v>57.86449999999999</v>
       </c>
       <c r="AH12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>305.532</v>
+        <v>65.78279999999999</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>325.3349999999999</v>
+        <v>70.387596</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>266.6</v>
+        <v>60.95</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP12" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AQ12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R2-BATAINDIA-IND-20260804-21b729</t>
+          <t>R1-VLO-USA-20260903-19ab39</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260804</t>
+          <t>VLO_USA_20260903</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2358,53 +2468,59 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Bata India</t>
-        </is>
-      </c>
+          <t>VLO</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #8 · Conf 52% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>24</v>
+        <v>51.7</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2412,58 +2528,54 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>-30.3</v>
+        <v>59.2</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB13" s="3" t="inlineStr"/>
       <c r="AC13" s="3" t="n">
-        <v>709</v>
+        <v>366.09</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>709</v>
+        <v>366.09</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>701.91</v>
+        <v>362.43</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>716.09</v>
+        <v>369.75</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>673.55</v>
+        <v>347.7855</v>
       </c>
       <c r="AH13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>765.72</v>
+        <v>410.02</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>815.3499999999999</v>
+        <v>438.7214</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>677.35</v>
+        <v>361.99</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>-1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>0</v>
@@ -2472,29 +2584,35 @@
         <v>0</v>
       </c>
       <c r="AQ13" s="3" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU13" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
+          <t>R1-GRMN-USA-20260903-5399b1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT_IND_20260805</t>
+          <t>GRMN_USA_20260903</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2504,17 +2622,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -2526,27 +2644,37 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>40.7</v>
+        <v>48.9</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2554,89 +2682,91 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>23.8</v>
+        <v>49.2</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB14" s="3" t="inlineStr"/>
       <c r="AC14" s="3" t="n">
-        <v>5322.4</v>
+        <v>276.04</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>5322.4</v>
+        <v>276.04</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>5269.18</v>
+        <v>270.52</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>5375.62</v>
+        <v>281.56</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>5056.28</v>
+        <v>262.238</v>
       </c>
       <c r="AH14" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>5748.192</v>
+        <v>298.1232000000001</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>6120.759999999999</v>
+        <v>318.9918240000001</v>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>5800</v>
+        <v>275.17</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>-1.9</v>
+        <v>0.32</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP14" s="3" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
+          <t>R1-GOOG-USA-20260903-9de97a</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG_IND_20260805</t>
+          <t>GOOG_USA_20260903</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2646,17 +2776,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -2670,25 +2800,35 @@
       <c r="K15" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>38.3</v>
+        <v>48.9</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2696,89 +2836,91 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>20.7</v>
+        <v>47.9</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB15" s="3" t="inlineStr"/>
       <c r="AC15" s="3" t="n">
-        <v>11127</v>
+        <v>333.78</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>11127</v>
+        <v>333.78</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>11015.73</v>
+        <v>327.1</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>11238.27</v>
+        <v>340.46</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>10570.65</v>
+        <v>317.091</v>
       </c>
       <c r="AH15" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>12017.16</v>
+        <v>360.4824</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>12796.05</v>
+        <v>385.716168</v>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>11333</v>
+        <v>332.03</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-0.2</v>
+        <v>0.53</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP15" s="3" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AQ15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-LICI-IND-20260805-a4f409</t>
+          <t>R2-TRV-USA-20260810-a2c57b</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LICI_IND_20260805</t>
+          <t>TRV_USA_20260810</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2788,7 +2930,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2798,10 +2940,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2810,10 +2956,14 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr"/>
@@ -2821,12 +2971,12 @@
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>37.2</v>
+        <v>56.8</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2834,11 +2984,11 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>20.6</v>
+        <v>29.2</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>60</v>
@@ -2848,75 +2998,47 @@
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC16" s="3" t="n">
-        <v>391.3</v>
-      </c>
-      <c r="AD16" s="3" t="n">
-        <v>391.3</v>
-      </c>
-      <c r="AE16" s="3" t="n">
-        <v>387.39</v>
-      </c>
-      <c r="AF16" s="3" t="n">
-        <v>395.21</v>
-      </c>
-      <c r="AG16" s="3" t="n">
-        <v>371.735</v>
-      </c>
-      <c r="AH16" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI16" s="3" t="n">
-        <v>422.604</v>
-      </c>
-      <c r="AJ16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK16" s="3" t="n">
-        <v>449.995</v>
-      </c>
-      <c r="AL16" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr"/>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
       <c r="AM16" s="3" t="n">
-        <v>412.15</v>
+        <v>363.92</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="AO16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr"/>
       <c r="AS16" s="3" t="inlineStr"/>
       <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU16" s="3" t="inlineStr"/>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R2-TIINDIA-IND-20260805-44fbae</t>
+          <t>R2-V-USA-20260810-1697f4</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA_IND_20260805</t>
+          <t>V_USA_20260810</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2926,7 +3048,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2936,10 +3058,14 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2948,10 +3074,14 @@
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr"/>
@@ -2959,12 +3089,12 @@
       <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>21.5</v>
+        <v>53.6</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -2972,11 +3102,11 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>-25.9</v>
+        <v>27.8</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>60</v>
@@ -2986,792 +3116,40 @@
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC17" s="3" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="AD17" s="3" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="AE17" s="3" t="n">
-        <v>2716.86</v>
-      </c>
-      <c r="AF17" s="3" t="n">
-        <v>2771.74</v>
-      </c>
-      <c r="AG17" s="3" t="n">
-        <v>2607.085</v>
-      </c>
-      <c r="AH17" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI17" s="3" t="n">
-        <v>2963.844000000001</v>
-      </c>
-      <c r="AJ17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>3155.945</v>
-      </c>
-      <c r="AL17" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr"/>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr"/>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr"/>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="n">
-        <v>2763.2</v>
+        <v>372.67</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="AO17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1.54</v>
+      </c>
+      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr"/>
       <c r="AS17" s="3" t="inlineStr"/>
       <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU17" s="3" t="inlineStr"/>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>R1-LUPIN-IND-20260903-4a3928</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>LUPIN_IND_20260903</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Lupin</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-11.8%) · Rank → 3→3 · Conf 72% · momentum → · band HOLD · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-10.9% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA18" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB18" s="3" t="inlineStr"/>
-      <c r="AC18" s="3" t="n">
-        <v>2153</v>
-      </c>
-      <c r="AD18" s="3" t="n">
-        <v>2417</v>
-      </c>
-      <c r="AE18" s="3" t="n">
-        <v>2392.83</v>
-      </c>
-      <c r="AF18" s="3" t="n">
-        <v>2441.17</v>
-      </c>
-      <c r="AG18" s="3" t="n">
-        <v>2296.15</v>
-      </c>
-      <c r="AH18" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI18" s="3" t="n">
-        <v>2610.36</v>
-      </c>
-      <c r="AJ18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>2779.55</v>
-      </c>
-      <c r="AL18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM18" s="3" t="n">
-        <v>2160.2</v>
-      </c>
-      <c r="AN18" s="3" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="AO18" s="3" t="n">
-        <v>-10.92</v>
-      </c>
-      <c r="AP18" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ18" s="3" t="n">
-        <v>-10.92</v>
-      </c>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>R1-PIDILITIND-IND-20260903-ef7fb3</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>PIDILITIND_IND_20260903</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Pidilite</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="X19" s="3" t="inlineStr"/>
-      <c r="Y19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA19" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="3" t="n">
-        <v>1625.5</v>
-      </c>
-      <c r="AD19" s="3" t="n">
-        <v>1625.5</v>
-      </c>
-      <c r="AE19" s="3" t="n">
-        <v>1609.24</v>
-      </c>
-      <c r="AF19" s="3" t="n">
-        <v>1641.76</v>
-      </c>
-      <c r="AG19" s="3" t="n">
-        <v>1544.225</v>
-      </c>
-      <c r="AH19" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI19" s="3" t="n">
-        <v>1755.54</v>
-      </c>
-      <c r="AJ19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>1869.325</v>
-      </c>
-      <c r="AL19" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM19" s="3" t="n">
-        <v>1617.2</v>
-      </c>
-      <c r="AN19" s="3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AO19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>R1-KOTAKBANK-IND-20260903-242281</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>KOTAKBANK_IND_20260903</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Kotak Bank</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr"/>
-      <c r="U20" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="X20" s="3" t="inlineStr"/>
-      <c r="Y20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA20" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB20" s="3" t="inlineStr"/>
-      <c r="AC20" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="AD20" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="AE20" s="3" t="n">
-        <v>385.41</v>
-      </c>
-      <c r="AF20" s="3" t="n">
-        <v>393.19</v>
-      </c>
-      <c r="AG20" s="3" t="n">
-        <v>369.835</v>
-      </c>
-      <c r="AH20" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI20" s="3" t="n">
-        <v>420.444</v>
-      </c>
-      <c r="AJ20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK20" s="3" t="n">
-        <v>447.695</v>
-      </c>
-      <c r="AL20" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM20" s="3" t="n">
-        <v>422.8</v>
-      </c>
-      <c r="AN20" s="3" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AO20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr"/>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>R1-BRITANNIA-IND-20260903-c0907a</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA_IND_20260903</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="X21" s="3" t="inlineStr"/>
-      <c r="Y21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA21" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB21" s="3" t="inlineStr"/>
-      <c r="AC21" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AD21" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AE21" s="3" t="n">
-        <v>5351.94</v>
-      </c>
-      <c r="AF21" s="3" t="n">
-        <v>5460.06</v>
-      </c>
-      <c r="AG21" s="3" t="n">
-        <v>5135.7</v>
-      </c>
-      <c r="AH21" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI21" s="3" t="n">
-        <v>5838.48</v>
-      </c>
-      <c r="AJ21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK21" s="3" t="n">
-        <v>6216.9</v>
-      </c>
-      <c r="AL21" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM21" s="3" t="n">
-        <v>5187</v>
-      </c>
-      <c r="AN21" s="3" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="AO21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr"/>
-      <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>R1-TATAPOWER-IND-20260903-a6745f</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER_IND_20260903</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
-      <c r="O22" s="3" t="inlineStr"/>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr"/>
-      <c r="U22" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="X22" s="3" t="inlineStr"/>
-      <c r="Y22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA22" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB22" s="3" t="inlineStr"/>
-      <c r="AC22" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AD22" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AE22" s="3" t="n">
-        <v>377.78</v>
-      </c>
-      <c r="AF22" s="3" t="n">
-        <v>385.42</v>
-      </c>
-      <c r="AG22" s="3" t="n">
-        <v>362.52</v>
-      </c>
-      <c r="AH22" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI22" s="3" t="n">
-        <v>412.128</v>
-      </c>
-      <c r="AJ22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>438.84</v>
-      </c>
-      <c r="AL22" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM22" s="3" t="n">
-        <v>350.55</v>
-      </c>
-      <c r="AN22" s="3" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AO22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03 00:49</t>
+          <t>2026-09-03 12:29</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV22"/>
+  <autoFilter ref="A1:AV17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-09-03.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV17"/>
+  <dimension ref="A1:AV15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -770,12 +770,12 @@
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>73.3</v>
+        <v>75.8</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · band HOLD · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 49% · band HOLD · 17d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>31.7</v>
+        <v>34.8</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
@@ -828,40 +828,40 @@
         </is>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>169.46</v>
+        <v>177.65</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>169.46</v>
+        <v>177.65</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>167.77</v>
+        <v>175.88</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>171.15</v>
+        <v>179.43</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>159.29</v>
+        <v>166.99</v>
       </c>
       <c r="AH2" s="3" t="n">
         <v>-6</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>189.8</v>
+        <v>198.97</v>
       </c>
       <c r="AJ2" s="3" t="n">
         <v>12</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>210.13</v>
+        <v>220.29</v>
       </c>
       <c r="AL2" s="3" t="n">
         <v>24</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>179.92</v>
+        <v>169.46</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>-5.81</v>
+        <v>4.83</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
@@ -924,18 +924,24 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>→ HOOD · +5.5pp alpha</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K3" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="n">
-        <v>83.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -955,7 +961,7 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #7 · Conf 49% · band STRONG · 60d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #5 · Conf 49% · band STRONG · 17d left · → EXIT (rotate to HOOD)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
@@ -968,7 +974,7 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>28.1</v>
+        <v>29.7</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>1</v>
@@ -977,10 +983,10 @@
         <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
@@ -988,44 +994,42 @@
         </is>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>101.87</v>
+        <v>105.28</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>101.87</v>
+        <v>105.28</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>100.85</v>
+        <v>104.23</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>102.89</v>
+        <v>106.33</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>96.78</v>
+        <v>100.02</v>
       </c>
       <c r="AH3" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>110.02</v>
+        <v>113.7</v>
       </c>
       <c r="AJ3" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>117.15</v>
+        <v>121.07</v>
       </c>
       <c r="AL3" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>100.55</v>
+        <v>101.87</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AO3" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3.35</v>
+      </c>
+      <c r="AO3" s="3" t="inlineStr"/>
       <c r="AP3" s="3" t="n">
         <v>0</v>
       </c>
@@ -1040,23 +1044,23 @@
       <c r="AS3" s="3" t="inlineStr"/>
       <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R2-GOOG-USA-20260903-5f0aaa</t>
+          <t>R1-PLTR-USA-20260903-4ffe75</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GOOG_USA_20260903</t>
+          <t>PLTR_USA_20260903</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1071,35 +1075,29 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>→ PLTR · +5.8pp alpha</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="n">
-        <v>71.8</v>
+        <v>75.8</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -1107,7 +1105,7 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>-0.8</v>
@@ -1119,7 +1117,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #10 · Conf 49% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
@@ -1132,93 +1130,91 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB4" s="3" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>333.78</v>
+        <v>177.65</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>333.78</v>
+        <v>177.65</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>330.44</v>
+        <v>175.88</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>337.12</v>
+        <v>179.43</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>317.09</v>
+        <v>168.7675</v>
       </c>
       <c r="AH4" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>360.48</v>
+        <v>198.97</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>383.85</v>
+        <v>212.8979</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>332.03</v>
+        <v>169.46</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AO4" s="3" t="inlineStr"/>
+        <v>4.83</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>Growth · Quality · Mean Reversion</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU4" s="3" t="n">
-        <v>5.85</v>
+        <v>12</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R2-GM-USA-20260903-c02966</t>
+          <t>R1-UBER-USA-20260903-97a5e6</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>GM_USA_20260903</t>
+          <t>UBER_USA_20260903</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1233,43 +1229,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>→ PLTR · +57.6pp alpha</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>52.5</v>
+        <v>76.5</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>29.1</v>
+        <v>50.9</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>-0.8</v>
@@ -1281,12 +1271,12 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #11 · Conf 30% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 52% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>29.9</v>
+        <v>51.6</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1294,93 +1284,91 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-25.9</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="X5" s="3" t="inlineStr"/>
       <c r="Y5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB5" s="3" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>84.87</v>
+        <v>78.02</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>84.87</v>
+        <v>78.02</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>84.02</v>
+        <v>77.23</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>85.72</v>
+        <v>78.8</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>80.63</v>
+        <v>74.119</v>
       </c>
       <c r="AH5" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>91.66</v>
+        <v>87.38</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>93.4966</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>85.63</v>
+        <v>76.45</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="AO5" s="3" t="inlineStr"/>
+        <v>2.05</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU5" s="3" t="n">
-        <v>57.63</v>
+        <v>12</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-PLTR-USA-20260903-4ffe75</t>
+          <t>R1-HOOD-USA-20260903-0fb470</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PLTR_USA_20260903</t>
+          <t>HOOD_USA_20260903</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1400,7 +1388,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -1412,12 +1400,12 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="n">
-        <v>73.3</v>
+        <v>78.8</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -1437,7 +1425,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
@@ -1450,7 +1438,7 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>70.5</v>
+        <v>62.4</v>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="n">
@@ -1464,40 +1452,40 @@
       </c>
       <c r="AB6" s="3" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>169.46</v>
+        <v>117.17</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>169.46</v>
+        <v>117.17</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>167.77</v>
+        <v>116</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>171.15</v>
+        <v>118.35</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>160.987</v>
+        <v>111.3115</v>
       </c>
       <c r="AH6" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>189.8</v>
+        <v>131.24</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>12</v>
+        <v>12.01</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>203.086</v>
+        <v>140.4268</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>19.84</v>
+        <v>19.85</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>179.92</v>
+        <v>106.99</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>-5.81</v>
+        <v>9.52</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>0</v>
@@ -1518,23 +1506,23 @@
         <v>5</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>12</v>
+        <v>12.01</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-MU-USA-20260903-2c5556</t>
+          <t>R1-VLO-USA-20260903-19ab39</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MU_USA_20260903</t>
+          <t>VLO_USA_20260903</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1554,7 +1542,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1566,12 +1554,12 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="n">
-        <v>73.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -1579,7 +1567,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>48.1</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>-0.8</v>
@@ -1591,12 +1579,12 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 52% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>48.9</v>
+        <v>51.7</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1604,7 +1592,7 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>59.4</v>
       </c>
       <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
@@ -1618,40 +1606,40 @@
       </c>
       <c r="AB7" s="3" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>956.08</v>
+        <v>365.57</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>956.08</v>
+        <v>365.57</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>946.52</v>
+        <v>358.26</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>965.64</v>
+        <v>372.88</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>908.276</v>
+        <v>347.2915</v>
       </c>
       <c r="AH7" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>1070.81</v>
+        <v>394.8156</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>1145.7667</v>
+        <v>422.4526920000001</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>19.84</v>
+        <v>15.56</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>933.4400000000001</v>
+        <v>366.09</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>2.43</v>
+        <v>-0.14</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>0</v>
@@ -1672,23 +1660,23 @@
         <v>5</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-INCY-USA-20260903-c89a3c</t>
+          <t>R1-SNDK-USA-20260903-003517</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INCY_USA_20260903</t>
+          <t>SNDK_USA_20260903</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1708,7 +1696,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -1720,12 +1708,12 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="n">
-        <v>77.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -1733,7 +1721,7 @@
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>48.2</v>
+        <v>42.3</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>-0.8</v>
@@ -1745,12 +1733,12 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 43% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>48.9</v>
+        <v>43</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1758,7 +1746,7 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>67.5</v>
+        <v>53.2</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
@@ -1772,40 +1760,40 @@
       </c>
       <c r="AB8" s="3" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>128.83</v>
+        <v>1523.76</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>128.83</v>
+        <v>1523.76</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>126.25</v>
+        <v>1493.28</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>131.41</v>
+        <v>1554.24</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>122.3885</v>
+        <v>1447.572</v>
       </c>
       <c r="AH8" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>139.1364</v>
+        <v>1645.6608</v>
       </c>
       <c r="AJ8" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>148.875948</v>
+        <v>1760.857056</v>
       </c>
       <c r="AL8" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>125.01</v>
+        <v>1553.4</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>3.06</v>
+        <v>-1.91</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>0</v>
@@ -1830,19 +1818,19 @@
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-UBER-USA-20260903-97a5e6</t>
+          <t>R1-GRMN-USA-20260903-5399b1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>UBER_USA_20260903</t>
+          <t>GRMN_USA_20260903</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1862,24 +1850,24 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -1887,7 +1875,7 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>50.9</v>
+        <v>48.1</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>-0.8</v>
@@ -1899,12 +1887,12 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 52% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>51.6</v>
+        <v>48.9</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1912,7 +1900,7 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>66.3</v>
+        <v>49.3</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
@@ -1926,40 +1914,40 @@
       </c>
       <c r="AB9" s="3" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>76.45</v>
+        <v>278.52</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>76.45</v>
+        <v>278.52</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>74.92</v>
+        <v>272.95</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>77.98</v>
+        <v>284.09</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>72.6275</v>
+        <v>264.594</v>
       </c>
       <c r="AH9" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>82.566</v>
+        <v>300.8016</v>
       </c>
       <c r="AJ9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>88.34562000000001</v>
+        <v>321.857712</v>
       </c>
       <c r="AL9" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>75.23999999999999</v>
+        <v>276.04</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>1.61</v>
+        <v>0.9</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>0</v>
@@ -1984,19 +1972,19 @@
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-HOOD-USA-20260903-0fb470</t>
+          <t>R1-INCY-USA-20260903-c89a3c</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>HOOD_USA_20260903</t>
+          <t>INCY_USA_20260903</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2016,24 +2004,24 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2053,7 +2041,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
@@ -2066,7 +2054,7 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>63.5</v>
+        <v>48.4</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
@@ -2080,40 +2068,40 @@
       </c>
       <c r="AB10" s="3" t="inlineStr"/>
       <c r="AC10" s="3" t="n">
-        <v>106.99</v>
+        <v>128.32</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>106.99</v>
+        <v>128.32</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>104.85</v>
+        <v>125.75</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>109.13</v>
+        <v>130.89</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>101.6405</v>
+        <v>121.904</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>115.5492</v>
+        <v>138.5856</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>123.637644</v>
+        <v>148.286592</v>
       </c>
       <c r="AL10" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>103.51</v>
+        <v>128.83</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>3.36</v>
+        <v>-0.4</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>0</v>
@@ -2138,19 +2126,19 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R1-GDDY-USA-20260903-41a3ad</t>
+          <t>R1-GOOG-USA-20260903-9de97a</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>GDDY_USA_20260903</t>
+          <t>GOOG_USA_20260903</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2170,24 +2158,24 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="n">
-        <v>83.8</v>
+        <v>71.5</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2195,7 +2183,7 @@
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>-0.8</v>
@@ -2207,7 +2195,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 49% · momentum → · band STRONG · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
@@ -2220,7 +2208,7 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>61.1</v>
+        <v>48.1</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
@@ -2234,40 +2222,40 @@
       </c>
       <c r="AB11" s="3" t="inlineStr"/>
       <c r="AC11" s="3" t="n">
-        <v>101.87</v>
+        <v>339.35</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>101.87</v>
+        <v>339.35</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>99.83</v>
+        <v>332.56</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>103.91</v>
+        <v>346.14</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>96.7765</v>
+        <v>322.3825</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>110.0196</v>
+        <v>366.498</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>117.720972</v>
+        <v>392.1528600000001</v>
       </c>
       <c r="AL11" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>100.55</v>
+        <v>333.78</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>0</v>
@@ -2292,7 +2280,7 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
@@ -2330,18 +2318,18 @@
       <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2361,7 +2349,7 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 55% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 55% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
@@ -2374,7 +2362,7 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>60.4</v>
+        <v>40.7</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
@@ -2388,37 +2376,37 @@
       </c>
       <c r="AB12" s="3" t="inlineStr"/>
       <c r="AC12" s="3" t="n">
-        <v>60.91</v>
+        <v>60.87</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>60.91</v>
+        <v>60.87</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>59.69</v>
+        <v>59.65</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>62.13</v>
+        <v>62.09</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>57.86449999999999</v>
+        <v>57.8265</v>
       </c>
       <c r="AH12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>65.78279999999999</v>
+        <v>65.7396</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>70.387596</v>
+        <v>70.34137199999999</v>
       </c>
       <c r="AL12" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>60.95</v>
+        <v>60.91</v>
       </c>
       <c r="AN12" s="3" t="n">
         <v>-0.07000000000000001</v>
@@ -2446,19 +2434,19 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R1-VLO-USA-20260903-19ab39</t>
+          <t>R1-GDDY-USA-20260903-41a3ad</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>VLO_USA_20260903</t>
+          <t>GDDY_USA_20260903</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2478,24 +2466,24 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="n">
-        <v>81.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -2503,7 +2491,7 @@
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>51</v>
+        <v>48.2</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>-0.8</v>
@@ -2515,12 +2503,12 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #8 · Conf 52% · momentum → · band STRONG · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 49% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>51.7</v>
+        <v>48.9</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2528,7 +2516,7 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>59.2</v>
+        <v>40.5</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
@@ -2542,40 +2530,40 @@
       </c>
       <c r="AB13" s="3" t="inlineStr"/>
       <c r="AC13" s="3" t="n">
-        <v>366.09</v>
+        <v>105.28</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>366.09</v>
+        <v>105.28</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>362.43</v>
+        <v>103.17</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>369.75</v>
+        <v>107.39</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>347.7855</v>
+        <v>100.016</v>
       </c>
       <c r="AH13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>410.02</v>
+        <v>113.7024</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>438.7214</v>
+        <v>121.661568</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>19.84</v>
+        <v>15.56</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>361.99</v>
+        <v>101.87</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>1.13</v>
+        <v>3.35</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>0</v>
@@ -2596,23 +2584,23 @@
         <v>5</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R1-GRMN-USA-20260903-5399b1</t>
+          <t>R2-TRV-USA-20260810-a2c57b</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>GRMN_USA_20260903</t>
+          <t>TRV_USA_20260810</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2627,15 +2615,19 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>GRMN</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2644,37 +2636,27 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>48.9</v>
+        <v>56.8</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2682,91 +2664,61 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>49.2</v>
+        <v>29.2</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="n">
-        <v>276.04</v>
-      </c>
-      <c r="AD14" s="3" t="n">
-        <v>276.04</v>
-      </c>
-      <c r="AE14" s="3" t="n">
-        <v>270.52</v>
-      </c>
-      <c r="AF14" s="3" t="n">
-        <v>281.56</v>
-      </c>
-      <c r="AG14" s="3" t="n">
-        <v>262.238</v>
-      </c>
-      <c r="AH14" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI14" s="3" t="n">
-        <v>298.1232000000001</v>
-      </c>
-      <c r="AJ14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK14" s="3" t="n">
-        <v>318.9918240000001</v>
-      </c>
-      <c r="AL14" s="3" t="n">
-        <v>15.56</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="n">
-        <v>275.17</v>
+        <v>366.18</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AO14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1.31</v>
+      </c>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU14" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AS14" s="3" t="inlineStr"/>
+      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AU14" s="3" t="inlineStr"/>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R1-GOOG-USA-20260903-9de97a</t>
+          <t>R2-V-USA-20260810-1697f4</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>GOOG_USA_20260903</t>
+          <t>V_USA_20260810</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2781,15 +2733,19 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2798,37 +2754,27 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>48.9</v>
+        <v>53.6</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2836,320 +2782,54 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>47.9</v>
+        <v>27.8</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="n">
-        <v>333.78</v>
-      </c>
-      <c r="AD15" s="3" t="n">
-        <v>333.78</v>
-      </c>
-      <c r="AE15" s="3" t="n">
-        <v>327.1</v>
-      </c>
-      <c r="AF15" s="3" t="n">
-        <v>340.46</v>
-      </c>
-      <c r="AG15" s="3" t="n">
-        <v>317.091</v>
-      </c>
-      <c r="AH15" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI15" s="3" t="n">
-        <v>360.4824</v>
-      </c>
-      <c r="AJ15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK15" s="3" t="n">
-        <v>385.716168</v>
-      </c>
-      <c r="AL15" s="3" t="n">
-        <v>15.56</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
       <c r="AM15" s="3" t="n">
-        <v>332.03</v>
+        <v>378.4</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AO15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.92</v>
+      </c>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU15" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AS15" s="3" t="inlineStr"/>
+      <c r="AT15" s="3" t="inlineStr"/>
+      <c r="AU15" s="3" t="inlineStr"/>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>R2-TRV-USA-20260810-a2c57b</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>TRV_USA_20260810</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="X16" s="3" t="inlineStr"/>
-      <c r="Y16" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z16" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA16" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AC16" s="3" t="inlineStr"/>
-      <c r="AD16" s="3" t="inlineStr"/>
-      <c r="AE16" s="3" t="inlineStr"/>
-      <c r="AF16" s="3" t="inlineStr"/>
-      <c r="AG16" s="3" t="inlineStr"/>
-      <c r="AH16" s="3" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
-      <c r="AM16" s="3" t="n">
-        <v>363.92</v>
-      </c>
-      <c r="AN16" s="3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AO16" s="3" t="inlineStr"/>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
-      <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>R2-V-USA-20260810-1697f4</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>V_USA_20260810</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="3" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="X17" s="3" t="inlineStr"/>
-      <c r="Y17" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA17" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AC17" s="3" t="inlineStr"/>
-      <c r="AD17" s="3" t="inlineStr"/>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="n">
-        <v>372.67</v>
-      </c>
-      <c r="AN17" s="3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:29</t>
+          <t>2026-09-03 13:50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV17"/>
+  <autoFilter ref="A1:AV15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>